--- a/materials/lab1/작업방법참고.xlsx
+++ b/materials/lab1/작업방법참고.xlsx
@@ -1,190 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI_Agent_tutor\Part2\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55E81C3A-BB51-492E-99A2-FD22DD63A873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="31920" xr2:uid="{4B463F6E-6F4F-4B30-8687-48EDE98CB26B}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="31920" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="작업방법" sheetId="1" r:id="rId1"/>
-    <sheet name="참고" sheetId="2" r:id="rId2"/>
+    <sheet name="작업방법" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="참고" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
-  <si>
-    <t>주문종합 시트 작성 방법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>표준 컬럼(7칸): 주문번호, 고객명, 상품명, 수량, 금액_원, 주문일, 주문채널</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 데이터 폴더에 들어있는 웹주문, 전화주문, 제휴주문 파일의 데이터를 모아서 주문종합 파일을 생성합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 세 원본 파일(웹주문/전화주문/제휴주문) 중 어느 한 곳에라도 있는 주문은 절대 빠뜨리지 않습니다.</t>
-  </si>
-  <si>
-    <t>- 같은 주문번호가 여러 파일에 겹쳐 등장하면 하나로 합치되, 어느 채널에서 가져왔는지 주문채널에 기록합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 수량과 매출액은 1000단위 구분기호(,)를 사용하여 나타냅니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 주문일은 반드시 YYYY-MM-DD 형식으로 통일합니다 (예: 2026-01-06).</t>
-  </si>
-  <si>
-    <t>- 금액이 원본에서 비어있는 경우 임의로 0을 채우지 말고 빈칸으로 남겨둡니다 (없는 값을 지어내지 않습니다).</t>
-  </si>
-  <si>
-    <t>종합</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>웹주문</t>
-  </si>
-  <si>
-    <t>전화주문</t>
-  </si>
-  <si>
-    <t>제휴주문</t>
-  </si>
-  <si>
-    <t>주문번호</t>
-  </si>
-  <si>
-    <t>order_id</t>
-  </si>
-  <si>
-    <t>협력사주문ID</t>
-  </si>
-  <si>
-    <t>고객명</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>구매자</t>
-  </si>
-  <si>
-    <t>상품명</t>
-  </si>
-  <si>
-    <t>상품</t>
-  </si>
-  <si>
-    <t>item</t>
-  </si>
-  <si>
-    <t>품목</t>
-  </si>
-  <si>
-    <t>수량</t>
-  </si>
-  <si>
-    <t>qty</t>
-  </si>
-  <si>
-    <t>개수</t>
-  </si>
-  <si>
-    <t>매출액</t>
-  </si>
-  <si>
-    <t>금액</t>
-  </si>
-  <si>
-    <t>amount</t>
-  </si>
-  <si>
-    <t>결제액</t>
-  </si>
-  <si>
-    <t>주문일자</t>
-  </si>
-  <si>
-    <t>주문일시</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>일자</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -203,31 +69,90 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -515,164 +440,243 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A470710-0622-442D-BF41-C634F5CC9F20}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>7</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>주문종합 시트 작성 방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>표준 컬럼(7칸): 주문번호, 고객명, 상품명, 수량, 금액_원, 주문일, 주문채널</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>- 데이터 폴더에 들어있는 웹주문, 전화주문, 제휴주문 파일의 데이터를 모아서 주문종합 파일을 생성합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>- 세 원본 파일(웹주문/전화주문/제휴주문) 중 어느 한 곳에라도 있는 주문은 절대 빠뜨리지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>- 같은 주문번호가 여러 파일에 겹쳐 등장하면 하나로 합치되, 어느 채널에서 가져왔는지 주문채널에 기록합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>- 수량과 매출액은 1000단위 구분기호(,)를 사용하여 나타냅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>- 주문일은 반드시 YYYY-MM-DD 형식으로 통일합니다 (예: 2026-01-06).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>- 금액이 원본에서 비어있는 경우 임의로 0을 채우지 말고 빈칸으로 남겨둡니다 (없는 값을 지어내지 않습니다).</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52230052-4DDA-4948-8095-9BFC62CF9301}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="4" width="13.125" customWidth="1"/>
+    <col width="13.125" customWidth="1" min="1" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>32</v>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>종합</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>웹주문</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>전화주문</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>제휴주문</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>주문번호</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>주문번호</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>order_id</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>협력사주문ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>고객명</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>고객명</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>구매자</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>품목</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>qty</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>개수</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>금액_원</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>결제액</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>주문일</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>주문일시</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>